--- a/database/template-import-export/templates/template-lumbung.xlsx
+++ b/database/template-import-export/templates/template-lumbung.xlsx
@@ -24,7 +24,7 @@
     <t>Jumlah &amp; kapasitas lumbung pangan dan gudang per kecamatan per tahun.</t>
   </si>
   <si>
-    <t>Dibuat otomatis: 22/9/2026, 14.21.33</t>
+    <t>Dibuat otomatis: 29/9/2026, 15.29.43</t>
   </si>
   <si>
     <t>CARA PAKAI</t>
